--- a/data/trans_camb/IP18A05-Dificultad-trans_camb.xlsx
+++ b/data/trans_camb/IP18A05-Dificultad-trans_camb.xlsx
@@ -40,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -66,13 +66,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -513,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -524,9 +517,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -542,68 +532,50 @@
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Niña</t>
         </is>
       </c>
-      <c r="G1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012/2007</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
     </row>
@@ -616,9 +588,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -631,15 +600,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr"/>
-      <c r="K4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="n">
+        <v>0.402172228324597</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>7.471801046319797</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>1.007404526464976</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>9.308619591778932</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>0.6905274279727054</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>8.273552308783092</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
@@ -648,15 +626,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr"/>
-      <c r="D5" s="5" t="inlineStr"/>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="5" t="inlineStr"/>
-      <c r="G5" s="5" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr"/>
-      <c r="J5" s="5" t="inlineStr"/>
-      <c r="K5" s="5" t="inlineStr"/>
+      <c r="C5" s="5" t="n">
+        <v>-0.6862280858957636</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-0.328196942780889</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-0.3338260423739059</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-0.5777180781629677</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>-0.3027143078898789</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>2.084241404363357</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
@@ -665,15 +652,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="n">
+        <v>2.28689954952779</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>26.86294932207834</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>3.198029249524264</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>32.04308137565551</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>1.841582133290966</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>20.59718874376581</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
@@ -682,15 +678,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="6" t="inlineStr"/>
-      <c r="I7" s="6" t="inlineStr"/>
-      <c r="J7" s="6" t="inlineStr"/>
-      <c r="K7" s="6" t="inlineStr"/>
+      <c r="C7" s="6" t="n">
+        <v>0.652833821652646</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>12.12874507028426</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>1.733085903137225</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>16.01406085476818</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>1.152865147557481</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>13.81305031038793</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
@@ -701,13 +706,16 @@
       </c>
       <c r="C8" s="6" t="inlineStr"/>
       <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="6" t="inlineStr"/>
+      <c r="E8" s="6" t="n">
+        <v>-0.667973396493867</v>
+      </c>
       <c r="F8" s="6" t="inlineStr"/>
-      <c r="G8" s="6" t="inlineStr"/>
-      <c r="H8" s="6" t="inlineStr"/>
-      <c r="I8" s="6" t="inlineStr"/>
-      <c r="J8" s="6" t="inlineStr"/>
-      <c r="K8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="n">
+        <v>-0.5133544694939378</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
@@ -720,11 +728,12 @@
       <c r="D9" s="6" t="inlineStr"/>
       <c r="E9" s="6" t="inlineStr"/>
       <c r="F9" s="6" t="inlineStr"/>
-      <c r="G9" s="6" t="inlineStr"/>
-      <c r="H9" s="6" t="inlineStr"/>
-      <c r="I9" s="6" t="inlineStr"/>
-      <c r="J9" s="6" t="inlineStr"/>
-      <c r="K9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="n">
+        <v>8.518787143992309</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>74.63157244326939</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -737,15 +746,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="5" t="inlineStr"/>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="5" t="inlineStr"/>
-      <c r="K10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="n">
+        <v>2.064723244050862</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>2.897650499789709</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-0.0660232878911855</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>2.573083852462115</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>0.9897913307141305</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>2.692121149881598</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
@@ -754,15 +772,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="5" t="inlineStr"/>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="5" t="inlineStr"/>
-      <c r="K11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="n">
+        <v>0.2052104264099553</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-0.4831727145679061</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-1.951150784724968</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-1.071697259401265</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>-0.5598486066642696</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>-0.1143774676195335</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
@@ -771,15 +798,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr"/>
-      <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="5" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr"/>
-      <c r="J12" s="5" t="inlineStr"/>
-      <c r="K12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="n">
+        <v>4.662321249941598</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>13.87027353657701</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>1.647605829521005</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>12.95626406444473</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>2.59474715766301</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>9.636292932858233</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
@@ -788,15 +824,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr"/>
-      <c r="D13" s="6" t="inlineStr"/>
-      <c r="E13" s="6" t="inlineStr"/>
-      <c r="F13" s="6" t="inlineStr"/>
-      <c r="G13" s="6" t="inlineStr"/>
-      <c r="H13" s="6" t="inlineStr"/>
-      <c r="I13" s="6" t="inlineStr"/>
-      <c r="J13" s="6" t="inlineStr"/>
-      <c r="K13" s="6" t="inlineStr"/>
+      <c r="C13" s="6" t="n">
+        <v>3.24433406621235</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>4.553126553659032</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>-0.04761403952894983</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>1.855631856207363</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.9825838600937309</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>2.672517640038438</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
@@ -805,15 +850,20 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr"/>
+      <c r="C14" s="6" t="n">
+        <v>-0.6075987089834536</v>
+      </c>
       <c r="D14" s="6" t="inlineStr"/>
-      <c r="E14" s="6" t="inlineStr"/>
+      <c r="E14" s="6" t="n">
+        <v>-1</v>
+      </c>
       <c r="F14" s="6" t="inlineStr"/>
-      <c r="G14" s="6" t="inlineStr"/>
-      <c r="H14" s="6" t="inlineStr"/>
-      <c r="I14" s="6" t="inlineStr"/>
-      <c r="J14" s="6" t="inlineStr"/>
-      <c r="K14" s="6" t="inlineStr"/>
+      <c r="G14" s="6" t="n">
+        <v>-0.4468379889523372</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.5312885984438825</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
@@ -824,13 +874,16 @@
       </c>
       <c r="C15" s="6" t="inlineStr"/>
       <c r="D15" s="6" t="inlineStr"/>
-      <c r="E15" s="6" t="inlineStr"/>
+      <c r="E15" s="6" t="n">
+        <v>4.344062512591235</v>
+      </c>
       <c r="F15" s="6" t="inlineStr"/>
-      <c r="G15" s="6" t="inlineStr"/>
-      <c r="H15" s="6" t="inlineStr"/>
-      <c r="I15" s="6" t="inlineStr"/>
-      <c r="J15" s="6" t="inlineStr"/>
-      <c r="K15" s="6" t="inlineStr"/>
+      <c r="G15" s="6" t="n">
+        <v>5.922147707643238</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>16.81472795799367</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -843,15 +896,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr"/>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="inlineStr"/>
-      <c r="F16" s="5" t="inlineStr"/>
-      <c r="G16" s="5" t="inlineStr"/>
-      <c r="H16" s="5" t="inlineStr"/>
-      <c r="I16" s="5" t="inlineStr"/>
-      <c r="J16" s="5" t="inlineStr"/>
-      <c r="K16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="n">
+        <v>-0.7484795953156077</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>2.705442098885574</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.3561553325991086</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>1.023619626056626</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>-0.2305200580745652</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>2.133912181512275</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
@@ -860,15 +922,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr"/>
-      <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="5" t="inlineStr"/>
-      <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="5" t="inlineStr"/>
-      <c r="K17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="n">
+        <v>-3.675505012326542</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-2.071261932401354</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-1.330419884461438</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-1.015016216179899</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>-1.964542590727968</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>-0.904016737002431</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
@@ -877,15 +948,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr"/>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr"/>
-      <c r="F18" s="5" t="inlineStr"/>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr"/>
-      <c r="J18" s="5" t="inlineStr"/>
-      <c r="K18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="n">
+        <v>1.768517694610528</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>17.68363508310431</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>1.718890576142487</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>7.189432991083844</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>1.243253155582665</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>11.06187650108218</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
@@ -894,15 +974,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr"/>
-      <c r="D19" s="6" t="inlineStr"/>
-      <c r="E19" s="6" t="inlineStr"/>
-      <c r="F19" s="6" t="inlineStr"/>
-      <c r="G19" s="6" t="inlineStr"/>
-      <c r="H19" s="6" t="inlineStr"/>
-      <c r="I19" s="6" t="inlineStr"/>
-      <c r="J19" s="6" t="inlineStr"/>
-      <c r="K19" s="6" t="inlineStr"/>
+      <c r="C19" s="6" t="n">
+        <v>-0.3193146039814684</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>1.154189343045709</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>0.7007293257349489</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>2.013953532974605</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-0.159105401128859</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>1.472830418528905</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n"/>
@@ -915,11 +1004,12 @@
       <c r="D20" s="6" t="inlineStr"/>
       <c r="E20" s="6" t="inlineStr"/>
       <c r="F20" s="6" t="inlineStr"/>
-      <c r="G20" s="6" t="inlineStr"/>
-      <c r="H20" s="6" t="inlineStr"/>
-      <c r="I20" s="6" t="inlineStr"/>
-      <c r="J20" s="6" t="inlineStr"/>
-      <c r="K20" s="6" t="inlineStr"/>
+      <c r="G20" s="6" t="n">
+        <v>-0.8547193360121249</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
@@ -932,11 +1022,12 @@
       <c r="D21" s="6" t="inlineStr"/>
       <c r="E21" s="6" t="inlineStr"/>
       <c r="F21" s="6" t="inlineStr"/>
-      <c r="G21" s="6" t="inlineStr"/>
-      <c r="H21" s="6" t="inlineStr"/>
-      <c r="I21" s="6" t="inlineStr"/>
-      <c r="J21" s="6" t="inlineStr"/>
-      <c r="K21" s="6" t="inlineStr"/>
+      <c r="G21" s="6" t="n">
+        <v>2.274665900690153</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>16.33589519308863</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -949,15 +1040,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr"/>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="5" t="inlineStr"/>
-      <c r="G22" s="5" t="inlineStr"/>
-      <c r="H22" s="5" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr"/>
-      <c r="J22" s="5" t="inlineStr"/>
-      <c r="K22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="n">
+        <v>-1.705222870263075</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-1.705222870263075</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-0.966839719942841</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>-0.966839719942841</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>-1.373127511499222</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>-1.373127511499222</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n"/>
@@ -966,15 +1066,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr"/>
-      <c r="D23" s="5" t="inlineStr"/>
-      <c r="E23" s="5" t="inlineStr"/>
-      <c r="F23" s="5" t="inlineStr"/>
-      <c r="G23" s="5" t="inlineStr"/>
-      <c r="H23" s="5" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="5" t="inlineStr"/>
-      <c r="K23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="n">
+        <v>-5.963308325825721</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-5.262596530219513</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-5.288113170044471</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-5.27574743834587</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>-3.632881943659009</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>-4.088988228669495</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n"/>
@@ -983,15 +1092,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr"/>
-      <c r="D24" s="5" t="inlineStr"/>
-      <c r="E24" s="5" t="inlineStr"/>
-      <c r="F24" s="5" t="inlineStr"/>
-      <c r="G24" s="5" t="inlineStr"/>
-      <c r="H24" s="5" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr"/>
-      <c r="J24" s="5" t="inlineStr"/>
-      <c r="K24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>-0.4351707039107721</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>-0.4341158544431062</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n"/>
@@ -1000,15 +1118,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr"/>
-      <c r="D25" s="6" t="inlineStr"/>
-      <c r="E25" s="6" t="inlineStr"/>
-      <c r="F25" s="6" t="inlineStr"/>
-      <c r="G25" s="6" t="inlineStr"/>
-      <c r="H25" s="6" t="inlineStr"/>
-      <c r="I25" s="6" t="inlineStr"/>
-      <c r="J25" s="6" t="inlineStr"/>
-      <c r="K25" s="6" t="inlineStr"/>
+      <c r="C25" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n"/>
@@ -1023,9 +1150,6 @@
       <c r="F26" s="6" t="inlineStr"/>
       <c r="G26" s="6" t="inlineStr"/>
       <c r="H26" s="6" t="inlineStr"/>
-      <c r="I26" s="6" t="inlineStr"/>
-      <c r="J26" s="6" t="inlineStr"/>
-      <c r="K26" s="6" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n"/>
@@ -1040,9 +1164,6 @@
       <c r="F27" s="6" t="inlineStr"/>
       <c r="G27" s="6" t="inlineStr"/>
       <c r="H27" s="6" t="inlineStr"/>
-      <c r="I27" s="6" t="inlineStr"/>
-      <c r="J27" s="6" t="inlineStr"/>
-      <c r="K27" s="6" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -1055,15 +1176,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr"/>
-      <c r="D28" s="5" t="inlineStr"/>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="5" t="inlineStr"/>
-      <c r="G28" s="5" t="inlineStr"/>
-      <c r="H28" s="5" t="inlineStr"/>
-      <c r="I28" s="5" t="inlineStr"/>
-      <c r="J28" s="5" t="inlineStr"/>
-      <c r="K28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="n">
+        <v>0.2816030248413285</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>2.919509337371508</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>0.3061650826354874</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>2.191331785249911</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>0.2931466073081902</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>2.625305723201285</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n"/>
@@ -1072,15 +1202,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr"/>
-      <c r="D29" s="5" t="inlineStr"/>
-      <c r="E29" s="5" t="inlineStr"/>
-      <c r="F29" s="5" t="inlineStr"/>
-      <c r="G29" s="5" t="inlineStr"/>
-      <c r="H29" s="5" t="inlineStr"/>
-      <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr"/>
-      <c r="K29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="n">
+        <v>-0.6529801064936083</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>0.2009223537731657</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>-0.5863897149149091</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>0.04168048056300566</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>-0.3861323690755001</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>0.8446705039867939</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n"/>
@@ -1089,15 +1228,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr"/>
-      <c r="D30" s="5" t="inlineStr"/>
-      <c r="E30" s="5" t="inlineStr"/>
-      <c r="F30" s="5" t="inlineStr"/>
-      <c r="G30" s="5" t="inlineStr"/>
-      <c r="H30" s="5" t="inlineStr"/>
-      <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="5" t="inlineStr"/>
-      <c r="K30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="n">
+        <v>1.321706147250276</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>8.834170368087127</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>1.27629939482326</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>5.876464643452009</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>1.060699297200538</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>5.723666355477964</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n"/>
@@ -1106,15 +1254,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr"/>
-      <c r="D31" s="6" t="inlineStr"/>
-      <c r="E31" s="6" t="inlineStr"/>
-      <c r="F31" s="6" t="inlineStr"/>
-      <c r="G31" s="6" t="inlineStr"/>
-      <c r="H31" s="6" t="inlineStr"/>
-      <c r="I31" s="6" t="inlineStr"/>
-      <c r="J31" s="6" t="inlineStr"/>
-      <c r="K31" s="6" t="inlineStr"/>
+      <c r="C31" s="6" t="n">
+        <v>0.2440216968785262</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>2.529886257292576</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>0.3523645332757795</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>2.521997593962293</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>0.2887059525351516</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>2.585536965522425</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n"/>
@@ -1123,15 +1280,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr"/>
-      <c r="D32" s="6" t="inlineStr"/>
-      <c r="E32" s="6" t="inlineStr"/>
-      <c r="F32" s="6" t="inlineStr"/>
-      <c r="G32" s="6" t="inlineStr"/>
-      <c r="H32" s="6" t="inlineStr"/>
-      <c r="I32" s="6" t="inlineStr"/>
-      <c r="J32" s="6" t="inlineStr"/>
-      <c r="K32" s="6" t="inlineStr"/>
+      <c r="C32" s="6" t="n">
+        <v>-0.4822018162770285</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>-0.07422492081034013</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>-0.5064447945021524</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>-0.1805018261684628</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>-0.3213641245726639</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>0.5610553281528119</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n"/>
@@ -1140,15 +1306,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr"/>
-      <c r="D33" s="6" t="inlineStr"/>
-      <c r="E33" s="6" t="inlineStr"/>
-      <c r="F33" s="6" t="inlineStr"/>
-      <c r="G33" s="6" t="inlineStr"/>
-      <c r="H33" s="6" t="inlineStr"/>
-      <c r="I33" s="6" t="inlineStr"/>
-      <c r="J33" s="6" t="inlineStr"/>
-      <c r="K33" s="6" t="inlineStr"/>
+      <c r="C33" s="6" t="n">
+        <v>1.879799354664582</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>10.82306178744944</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>2.88916253375459</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>11.63712039936268</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>1.44929292384989</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>7.592680048058451</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1159,11 +1334,11 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A22:A27"/>
     <mergeCell ref="A4:A9"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A10:A15"/>
     <mergeCell ref="A28:A33"/>
